--- a/excel/CDSCO_45kW_Ballast_MMS_Design_Calc.xlsx
+++ b/excel/CDSCO_45kW_Ballast_MMS_Design_Calc.xlsx
@@ -1036,7 +1036,7 @@
     <t xml:space="preserve">Overturning utilisation</t>
   </si>
   <si>
-    <t xml:space="preserve">R0 values are static (from the issued R0 calculation, git tag R0); R1 values are live formulas.</t>
+    <t xml:space="preserve">R0 values are static (from the issued R0 calculation, repo commit 09b5d58); R1 values are live formulas.</t>
   </si>
   <si>
     <t xml:space="preserve">1  INPUTS  -  all design inputs (yellow = editable)</t>
